--- a/Excel/pat_simmons.xlsx
+++ b/Excel/pat_simmons.xlsx
@@ -463,25 +463,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TzJCly4YgDQ</t>
+          <t>xU18PCIDQ8Y</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I Made Opus 4.8 and Fable 5 Build the Same App (RAW RESULTS)</t>
+          <t>Claude Code: in Terminal, in Cursor IDE, or in VS Code Extension?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>920146</v>
+        <v>47918</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0:21:12</t>
+          <t>0:18:15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,25 +493,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1njjOIiA8Kc</t>
+          <t>d3Glwdf_xA8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I Made GPT 5.6 and Fable 5 Build the Same App (RAW RESULTS)</t>
+          <t>Spec-Driven Development for AI Agents: I Tried OpenSpec and Others</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106733</v>
+        <v>39949</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0:26:26</t>
+          <t>0:28:13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,25 +523,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B9fFEucPNnA</t>
+          <t>DVlHZufvP10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Claude Fable 5: No Hype Full Breakdown &amp; Testing</t>
+          <t>I Tried Frontend-Design Plugin in Claude Code</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75625</v>
+        <v>32523</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0:10:14</t>
+          <t>0:06:10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,25 +553,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rdqgMNjvhMY</t>
+          <t>jf1sv2geEWo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT 5.6 Sol: No-Hype Full Review &amp; Testing</t>
+          <t>I Tested NEW Caveman AI Skill in Claude Code: Does it Really Save Tokens?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51290</v>
+        <v>30884</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0:40:04</t>
+          <t>0:06:06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,25 +583,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HhWwllcbc2g</t>
+          <t>0_-Ld5vtw8M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Claude Fable 5 Just Built the Ultimate Agent Harness</t>
+          <t>I Tried a NEW Claude Code /simplify Command to Improve Code</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>43670</v>
+        <v>23722</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0:19:21</t>
+          <t>0:07:41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -613,25 +613,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2PH9f6yM8KI</t>
+          <t>dThh2V7B9OQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fable 5 Is BACK. And It Just Built This Mobile App</t>
+          <t>I Tested New Sonnet 4.6 vs Opus 4.6: Speed, Token Usage, Code Quality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>41458</v>
+        <v>20549</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0:15:06</t>
+          <t>0:12:35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,25 +643,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f6C5wvXjn5k</t>
+          <t>rLNLa2dcjG8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I Tried Claude's New Dynamic Workflows (Honest Results)</t>
+          <t>I Tried "grill-me" Skill for Plan Mode. Wow.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>41433</v>
+        <v>19460</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0:12:49</t>
+          <t>0:11:13</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -673,25 +673,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MosF8v77YTw</t>
+          <t>4VqlpKCOeek</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Claude Sonnet 5: No Hype Full Breakdown &amp; Testing</t>
+          <t>I Tested New GLM-5 vs Opus and Sonnet. Wow.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24683</v>
+        <v>18308</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0:22:53</t>
+          <t>0:09:49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -703,25 +703,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>q4dqFC7hf1c</t>
+          <t>I6zy4HYbUuk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fable 5 Is BACK And It Just One Shotted THIS</t>
+          <t>Claude Code: Paste Image Screenshot into Prompt #claudecode #aicoding</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22469</v>
+        <v>18236</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0:07:07</t>
+          <t>0:00:48</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -733,25 +733,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>lPP6iBRuzgA</t>
+          <t>6vEsvX5_nPk</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimi K3 Is Here! (Better Than Opus 4.8?)</t>
+          <t>I Tried NEW Deepseek V4 Pro/Flash: Price, Speed, Quality Compared</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21899</v>
+        <v>16437</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0:36:06</t>
+          <t>0:17:17</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
